--- a/notebooks/Random Forest/predictions_afr_2019.xlsx
+++ b/notebooks/Random Forest/predictions_afr_2019.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>СКР_реальный</t>
+          <t>СКР</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -498,10 +498,10 @@
         <v>1.524</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08680047339733732</v>
+        <v>-0.0868004733973371</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.695569120560191</v>
+        <v>-5.695569120560177</v>
       </c>
     </row>
     <row r="4">
@@ -520,10 +520,10 @@
         <v>1.608</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03151228781115134</v>
+        <v>-0.03151228781115045</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.959719391240755</v>
+        <v>-1.9597193912407</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>1.666</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02114691222546439</v>
+        <v>-0.02114691222546394</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.269322462512869</v>
+        <v>-1.269322462512842</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>1.287</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.04761780317752162</v>
+        <v>-0.04761780317752229</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.699907006800437</v>
+        <v>-3.699907006800489</v>
       </c>
     </row>
     <row r="7">
@@ -586,10 +586,10 @@
         <v>1.319</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.055695894296935</v>
+        <v>-0.05569589429693522</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.222584859509857</v>
+        <v>-4.222584859509873</v>
       </c>
     </row>
     <row r="8">
@@ -608,10 +608,10 @@
         <v>1.324</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06996283144671134</v>
+        <v>-0.06996283144671089</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.284201770899648</v>
+        <v>-5.284201770899614</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>1.335550783063049</v>
+        <v>1.33555078306305</v>
       </c>
       <c r="D9" t="n">
         <v>1.239</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09655078306304876</v>
+        <v>-0.09655078306304943</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.792637858196025</v>
+        <v>-7.792637858196079</v>
       </c>
     </row>
     <row r="10">
@@ -674,10 +674,10 @@
         <v>1.257</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04221595099272402</v>
+        <v>-0.04221595099272379</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3584686549502</v>
+        <v>-3.358468654950183</v>
       </c>
     </row>
     <row r="12">
@@ -718,10 +718,10 @@
         <v>1.762</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04240093720867089</v>
+        <v>-0.04240093720867111</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.406409603216282</v>
+        <v>-2.406409603216294</v>
       </c>
     </row>
     <row r="14">
@@ -740,10 +740,10 @@
         <v>1.374</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.09181029747585279</v>
+        <v>-0.09181029747585256</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.681972159814613</v>
+        <v>-6.681972159814596</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>1.808548648850979</v>
+        <v>1.80854864885098</v>
       </c>
       <c r="D15" t="n">
         <v>1.758</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05054864885097898</v>
+        <v>-0.05054864885097987</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.875349763991979</v>
+        <v>-2.875349763992029</v>
       </c>
     </row>
     <row r="16">
@@ -784,10 +784,10 @@
         <v>1.436</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09961103325121434</v>
+        <v>-0.09961103325121368</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.936701479889579</v>
+        <v>-6.936701479889532</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         <v>2019</v>
       </c>
       <c r="C17" t="n">
-        <v>1.478246801437805</v>
+        <v>1.478246801437804</v>
       </c>
       <c r="D17" t="n">
         <v>1.375</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1032468014378047</v>
+        <v>-0.1032468014378041</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.508858286385799</v>
+        <v>-7.50885828638575</v>
       </c>
     </row>
     <row r="18">
@@ -828,10 +828,10 @@
         <v>1.359</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1420865093285844</v>
+        <v>-0.1420865093285841</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.45522511615779</v>
+        <v>-10.45522511615777</v>
       </c>
     </row>
     <row r="19">
@@ -850,10 +850,10 @@
         <v>1.665</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01541199848512464</v>
+        <v>0.01541199848512487</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9256455546621408</v>
+        <v>0.9256455546621541</v>
       </c>
     </row>
     <row r="20">
@@ -872,10 +872,10 @@
         <v>1.423</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02970623826374652</v>
+        <v>0.0297062382637463</v>
       </c>
       <c r="F20" t="n">
-        <v>2.087578233573192</v>
+        <v>2.087578233573176</v>
       </c>
     </row>
     <row r="21">
@@ -894,10 +894,10 @@
         <v>1.389</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08047971020202893</v>
+        <v>-0.08047971020202915</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.794075608497403</v>
+        <v>-5.794075608497419</v>
       </c>
     </row>
     <row r="22">
@@ -916,10 +916,10 @@
         <v>1.609</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0351539854446512</v>
+        <v>-0.03515398544465098</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.184834396808652</v>
+        <v>-2.184834396808638</v>
       </c>
     </row>
     <row r="23">
@@ -938,10 +938,10 @@
         <v>1.703</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01749430208455682</v>
+        <v>0.01749430208455727</v>
       </c>
       <c r="F23" t="n">
-        <v>1.027263774783137</v>
+        <v>1.027263774783163</v>
       </c>
     </row>
     <row r="24">
@@ -960,10 +960,10 @@
         <v>1.608</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.02137390746409817</v>
+        <v>-0.02137390746409773</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.32922310100113</v>
+        <v>-1.329223101001102</v>
       </c>
     </row>
     <row r="25">
@@ -982,10 +982,10 @@
         <v>1.495</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07951374424684521</v>
+        <v>-0.07951374424684454</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.318645100123425</v>
+        <v>-5.31864510012338</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>1.842568816258903</v>
+        <v>1.842568816258904</v>
       </c>
       <c r="D26" t="n">
         <v>1.786</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05656881625890331</v>
+        <v>-0.05656881625890398</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.167346934988987</v>
+        <v>-3.167346934989025</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         <v>2019</v>
       </c>
       <c r="C27" t="n">
-        <v>1.379878884730279</v>
+        <v>1.379878884730278</v>
       </c>
       <c r="D27" t="n">
         <v>1.351</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.02887888473027855</v>
+        <v>-0.02887888473027833</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.137593244284127</v>
+        <v>-2.137593244284111</v>
       </c>
     </row>
     <row r="28">
@@ -1042,16 +1042,16 @@
         <v>2019</v>
       </c>
       <c r="C28" t="n">
-        <v>1.072165354256853</v>
+        <v>1.072165354256854</v>
       </c>
       <c r="D28" t="n">
         <v>0.981</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.09116535425685346</v>
+        <v>-0.09116535425685368</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.293104409465185</v>
+        <v>-9.293104409465206</v>
       </c>
     </row>
     <row r="29">
@@ -1070,10 +1070,10 @@
         <v>1.338</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.04216928101170314</v>
+        <v>-0.04216928101170292</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.151665247511446</v>
+        <v>-3.151665247511429</v>
       </c>
     </row>
     <row r="30">
@@ -1092,10 +1092,10 @@
         <v>1.377</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.07167980754358649</v>
+        <v>-0.07167980754358605</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.205505268234313</v>
+        <v>-5.205505268234282</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>1.373458907016379</v>
+        <v>1.37345890701638</v>
       </c>
       <c r="D31" t="n">
         <v>1.233</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1404589070163789</v>
+        <v>-0.1404589070163795</v>
       </c>
       <c r="F31" t="n">
-        <v>-11.39163884966576</v>
+        <v>-11.39163884966582</v>
       </c>
     </row>
     <row r="32">
@@ -1136,10 +1136,10 @@
         <v>1.506</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.03403936213357639</v>
+        <v>-0.03403936213357572</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.260249809666427</v>
+        <v>-2.260249809666383</v>
       </c>
     </row>
     <row r="33">
@@ -1180,10 +1180,10 @@
         <v>1.389</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.08454950948972284</v>
+        <v>-0.08454950948972306</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.087077717042681</v>
+        <v>-6.087077717042697</v>
       </c>
     </row>
     <row r="35">
@@ -1246,10 +1246,10 @@
         <v>1.555</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.05881166010058947</v>
+        <v>-0.05881166010058858</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.782100328012185</v>
+        <v>-3.782100328012127</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>1.683064041941592</v>
+        <v>1.683064041941591</v>
       </c>
       <c r="D38" t="n">
         <v>1.624</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.05906404194159154</v>
+        <v>-0.05906404194159065</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.636948395418198</v>
+        <v>-3.636948395418143</v>
       </c>
     </row>
     <row r="39">
@@ -1312,10 +1312,10 @@
         <v>1.274</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.04443987827228857</v>
+        <v>-0.04443987827228923</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.488216504889213</v>
+        <v>-3.488216504889265</v>
       </c>
     </row>
     <row r="41">
@@ -1334,10 +1334,10 @@
         <v>1.589</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.07577844853070048</v>
+        <v>-0.07577844853070004</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.768939492177501</v>
+        <v>-4.768939492177473</v>
       </c>
     </row>
     <row r="42">
@@ -1356,10 +1356,10 @@
         <v>1.46</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.06038592928080289</v>
+        <v>-0.06038592928080311</v>
       </c>
       <c r="F42" t="n">
-        <v>-4.13602255347965</v>
+        <v>-4.136022553479665</v>
       </c>
     </row>
     <row r="43">
@@ -1378,10 +1378,10 @@
         <v>1.474</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.03753999450280987</v>
+        <v>-0.03753999450281031</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.546811024613967</v>
+        <v>-2.546811024613997</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1394,16 @@
         <v>2019</v>
       </c>
       <c r="C44" t="n">
-        <v>1.345411340445665</v>
+        <v>1.345411340445666</v>
       </c>
       <c r="D44" t="n">
         <v>1.253</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.09241134044566524</v>
+        <v>-0.09241134044566568</v>
       </c>
       <c r="F44" t="n">
-        <v>-7.375206739478471</v>
+        <v>-7.375206739478507</v>
       </c>
     </row>
     <row r="45">
@@ -1444,10 +1444,10 @@
         <v>1.497</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.08810044767387626</v>
+        <v>-0.08810044767387581</v>
       </c>
       <c r="F46" t="n">
-        <v>-5.885133445148714</v>
+        <v>-5.885133445148685</v>
       </c>
     </row>
     <row r="47">
@@ -1466,10 +1466,10 @@
         <v>1.854</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1115648714268898</v>
+        <v>-0.1115648714268902</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.017522730684453</v>
+        <v>-6.017522730684476</v>
       </c>
     </row>
     <row r="48">
@@ -1488,10 +1488,10 @@
         <v>1.788</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0414532211337999</v>
+        <v>-0.04145322113380034</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.31841281508948</v>
+        <v>-2.318412815089505</v>
       </c>
     </row>
     <row r="49">
@@ -1526,16 +1526,16 @@
         <v>2019</v>
       </c>
       <c r="C50" t="n">
-        <v>1.553544839170272</v>
+        <v>1.553544839170271</v>
       </c>
       <c r="D50" t="n">
         <v>1.537</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0165448391702725</v>
+        <v>-0.01654483917027139</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.076437161371015</v>
+        <v>-1.076437161370942</v>
       </c>
     </row>
     <row r="51">
@@ -1548,16 +1548,16 @@
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>1.667542852256844</v>
+        <v>1.667542852256843</v>
       </c>
       <c r="D51" t="n">
         <v>1.631</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.03654285225684362</v>
+        <v>-0.03654285225684273</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.240518225434924</v>
+        <v>-2.24051822543487</v>
       </c>
     </row>
     <row r="52">
@@ -1570,16 +1570,16 @@
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>1.651491156364978</v>
+        <v>1.651491156364977</v>
       </c>
       <c r="D52" t="n">
         <v>1.63</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.02149115636497823</v>
+        <v>-0.02149115636497734</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.318475850612161</v>
+        <v>-1.318475850612107</v>
       </c>
     </row>
     <row r="53">
@@ -1620,10 +1620,10 @@
         <v>1.496</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.06464175328948074</v>
+        <v>-0.06464175328948096</v>
       </c>
       <c r="F54" t="n">
-        <v>-4.320972813467963</v>
+        <v>-4.320972813467979</v>
       </c>
     </row>
     <row r="55">
@@ -1658,16 +1658,16 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>1.800590058156445</v>
+        <v>1.800590058156446</v>
       </c>
       <c r="D56" t="n">
         <v>1.773</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.02759005815644544</v>
+        <v>-0.02759005815644588</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.556122851463364</v>
+        <v>-1.556122851463389</v>
       </c>
     </row>
     <row r="57">
@@ -1686,10 +1686,10 @@
         <v>1.71</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.04362625691207866</v>
+        <v>-0.04362625691207889</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.551243094273606</v>
+        <v>-2.551243094273619</v>
       </c>
     </row>
     <row r="58">
@@ -1702,16 +1702,16 @@
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>1.565081659137522</v>
+        <v>1.565081659137521</v>
       </c>
       <c r="D58" t="n">
         <v>1.52</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.04508165913752205</v>
+        <v>-0.04508165913752116</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.965898627468556</v>
+        <v>-2.965898627468497</v>
       </c>
     </row>
     <row r="59">
@@ -1752,10 +1752,10 @@
         <v>1.579</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.08126218365771942</v>
+        <v>-0.08126218365771876</v>
       </c>
       <c r="F60" t="n">
-        <v>-5.146433417208323</v>
+        <v>-5.146433417208281</v>
       </c>
     </row>
     <row r="61">
@@ -1790,16 +1790,16 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>1.37631718801858</v>
+        <v>1.376317188018581</v>
       </c>
       <c r="D62" t="n">
         <v>1.345</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03131718801858052</v>
+        <v>-0.03131718801858097</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.328415466065466</v>
+        <v>-2.328415466065499</v>
       </c>
     </row>
     <row r="63">
@@ -1840,10 +1840,10 @@
         <v>1.235</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.05718656543805989</v>
+        <v>-0.05718656543805944</v>
       </c>
       <c r="F64" t="n">
-        <v>-4.630491128587845</v>
+        <v>-4.630491128587809</v>
       </c>
     </row>
     <row r="65">
@@ -1856,16 +1856,16 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>1.860945174031371</v>
+        <v>1.86094517403137</v>
       </c>
       <c r="D65" t="n">
         <v>1.877</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01605482596862928</v>
+        <v>0.01605482596862973</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8553450169754546</v>
+        <v>0.8553450169754782</v>
       </c>
     </row>
     <row r="66">
@@ -1884,10 +1884,10 @@
         <v>1.614</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.05293988749231815</v>
+        <v>-0.05293988749231771</v>
       </c>
       <c r="F66" t="n">
-        <v>-3.280042595558745</v>
+        <v>-3.280042595558717</v>
       </c>
     </row>
     <row r="67">
@@ -1906,10 +1906,10 @@
         <v>1.234</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.04772071482067508</v>
+        <v>-0.04772071482067486</v>
       </c>
       <c r="F67" t="n">
-        <v>-3.867156792599277</v>
+        <v>-3.867156792599259</v>
       </c>
     </row>
     <row r="68">
@@ -1994,10 +1994,10 @@
         <v>1.345</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.0481212789175236</v>
+        <v>-0.04812127891752427</v>
       </c>
       <c r="F71" t="n">
-        <v>-3.577790254090974</v>
+        <v>-3.577790254091024</v>
       </c>
     </row>
     <row r="72">
@@ -2038,10 +2038,10 @@
         <v>1.715</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.07301066776672571</v>
+        <v>-0.07301066776672638</v>
       </c>
       <c r="F73" t="n">
-        <v>-4.257181793978176</v>
+        <v>-4.257181793978215</v>
       </c>
     </row>
     <row r="74">
@@ -2054,16 +2054,16 @@
         <v>2019</v>
       </c>
       <c r="C74" t="n">
-        <v>1.596775583760227</v>
+        <v>1.596775583760226</v>
       </c>
       <c r="D74" t="n">
         <v>1.494</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1027755837602269</v>
+        <v>-0.1027755837602262</v>
       </c>
       <c r="F74" t="n">
-        <v>-6.879222473910769</v>
+        <v>-6.879222473910724</v>
       </c>
     </row>
     <row r="75">
@@ -2082,10 +2082,10 @@
         <v>1.425</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.05784624295075469</v>
+        <v>-0.05784624295075491</v>
       </c>
       <c r="F75" t="n">
-        <v>-4.059385470228399</v>
+        <v>-4.059385470228414</v>
       </c>
     </row>
     <row r="76">
@@ -2098,16 +2098,16 @@
         <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>1.552054330477505</v>
+        <v>1.552054330477504</v>
       </c>
       <c r="D76" t="n">
         <v>1.564</v>
       </c>
       <c r="E76" t="n">
-        <v>0.01194566952249554</v>
+        <v>0.01194566952249598</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7637896114127583</v>
+        <v>0.7637896114127866</v>
       </c>
     </row>
     <row r="77">
@@ -2126,10 +2126,10 @@
         <v>1.695</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0714699128121572</v>
+        <v>-0.07146991281215742</v>
       </c>
       <c r="F77" t="n">
-        <v>-4.216514030215763</v>
+        <v>-4.216514030215777</v>
       </c>
     </row>
     <row r="78">
@@ -2142,16 +2142,16 @@
         <v>2019</v>
       </c>
       <c r="C78" t="n">
-        <v>1.524307472964446</v>
+        <v>1.524307472964447</v>
       </c>
       <c r="D78" t="n">
         <v>1.474</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.05030747296444615</v>
+        <v>-0.05030747296444682</v>
       </c>
       <c r="F78" t="n">
-        <v>-3.412990024724976</v>
+        <v>-3.412990024725022</v>
       </c>
     </row>
     <row r="79">
@@ -2186,16 +2186,16 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>1.562457059954912</v>
+        <v>1.562457059954911</v>
       </c>
       <c r="D80" t="n">
         <v>1.495</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.06745705995491158</v>
+        <v>-0.06745705995491136</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.512177923405456</v>
+        <v>-4.512177923405441</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>1.946691365000847</v>
+        <v>1.946691365000848</v>
       </c>
       <c r="D81" t="n">
         <v>1.617</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3296913650008468</v>
+        <v>-0.3296913650008479</v>
       </c>
       <c r="F81" t="n">
-        <v>-20.38907637605732</v>
+        <v>-20.38907637605739</v>
       </c>
     </row>
     <row r="82">
@@ -2236,10 +2236,10 @@
         <v>1.805</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.06100674564940944</v>
+        <v>-0.061006745649409</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.379875105230441</v>
+        <v>-3.379875105230416</v>
       </c>
     </row>
     <row r="83">
@@ -2274,16 +2274,16 @@
         <v>2019</v>
       </c>
       <c r="C84" t="n">
-        <v>1.366072335569551</v>
+        <v>1.366072335569552</v>
       </c>
       <c r="D84" t="n">
         <v>1.43</v>
       </c>
       <c r="E84" t="n">
-        <v>0.06392766443044851</v>
+        <v>0.06392766443044806</v>
       </c>
       <c r="F84" t="n">
-        <v>4.470466044087308</v>
+        <v>4.470466044087277</v>
       </c>
     </row>
     <row r="85">
@@ -2302,10 +2302,10 @@
         <v>1.35</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.0460839172878087</v>
+        <v>-0.04608391728780914</v>
       </c>
       <c r="F85" t="n">
-        <v>-3.413623502800644</v>
+        <v>-3.413623502800677</v>
       </c>
     </row>
     <row r="86">
